--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,44 +920,130 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>368.12</v>
+      </c>
+      <c r="C12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="L12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="M12" t="n">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>317.08</v>
+      </c>
+      <c r="C13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="G13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="H13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="I13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="L13" t="n">
+        <v>35.23</v>
+      </c>
+      <c r="M13" t="n">
+        <v>35.23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>1748.16</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>207.78</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>129.57</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>164.11</v>
+      <c r="B14" s="1" t="n">
+        <v>2433.36</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="J14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <v>283.92</v>
+      </c>
+      <c r="L14" s="1" t="n">
+        <v>205.7</v>
+      </c>
+      <c r="M14" s="1" t="n">
+        <v>240.24</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,44 +1006,87 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="C14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M14" t="n">
+        <v>18.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>2433.36</v>
-      </c>
-      <c r="C14" s="1" t="n">
+      <c r="B15" s="1" t="n">
+        <v>2582.16</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="n">
         <v>283.92</v>
       </c>
-      <c r="D14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="H14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="I14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="J14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="L14" s="1" t="n">
-        <v>205.7</v>
-      </c>
-      <c r="M14" s="1" t="n">
-        <v>240.24</v>
+      <c r="G15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="I15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="J15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <v>302.52</v>
+      </c>
+      <c r="L15" s="1" t="n">
+        <v>224.3</v>
+      </c>
+      <c r="M15" s="1" t="n">
+        <v>258.84</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,44 +1049,87 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>174.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="D15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="I15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.77</v>
+      </c>
+      <c r="M15" t="n">
+        <v>21.77</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>2582.16</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1" t="n">
+      <c r="B16" s="1" t="n">
+        <v>2756.28</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
         <v>283.92</v>
       </c>
-      <c r="G15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="H15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="I15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="J15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1" t="n">
-        <v>302.52</v>
-      </c>
-      <c r="L15" s="1" t="n">
-        <v>224.3</v>
-      </c>
-      <c r="M15" s="1" t="n">
-        <v>258.84</v>
+      <c r="G16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>324.28</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>246.07</v>
+      </c>
+      <c r="M16" s="1" t="n">
+        <v>280.61</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,43 +1092,129 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>190.64</v>
+      </c>
+      <c r="C16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="D16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="G16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="H16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="I16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="L16" t="n">
+        <v>23.83</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>141.8</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="D17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>2756.28</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>283.92</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>324.28</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>246.07</v>
-      </c>
-      <c r="M16" s="1" t="n">
+      <c r="B18" s="1" t="n">
+        <v>3088.72</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>328</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>348.11</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>368.37</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>290.15</v>
+      </c>
+      <c r="M18" s="1" t="n">
         <v>280.61</v>
       </c>
     </row>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,44 +1178,87 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>176.04</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>22</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>22</v>
+      </c>
+      <c r="G18" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>22</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>22</v>
+      </c>
+      <c r="L18" t="n">
+        <v>22</v>
+      </c>
+      <c r="M18" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>3088.72</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>328</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="H18" s="1" t="n">
+      <c r="B19" s="1" t="n">
+        <v>3264.76</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>348.11</v>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>368.37</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>290.15</v>
-      </c>
-      <c r="M18" s="1" t="n">
-        <v>280.61</v>
+      <c r="I19" s="1" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>390.37</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>312.16</v>
+      </c>
+      <c r="M19" s="1" t="n">
+        <v>302.61</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,44 +1221,87 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>304.52</v>
+      </c>
+      <c r="C19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="D19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="G19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="H19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="I19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>38.06</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>3264.76</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>390.37</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>390.37</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>350.01</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>390.37</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>348.11</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>390.37</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>390.37</v>
-      </c>
-      <c r="L19" s="1" t="n">
+      <c r="B20" s="1" t="n">
+        <v>3569.28</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>388.07</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>386.18</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>428.44</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>312.16</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>302.61</v>
+      <c r="M20" s="1" t="n">
+        <v>340.68</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,80 +1228,123 @@
         <v>304.52</v>
       </c>
       <c r="C19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="D19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>38.06</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="H19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="I19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>38.06</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>314.12</v>
+      </c>
+      <c r="C20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="D20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="H20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="I20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>44.87</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>44.87</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>3569.28</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>428.44</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>428.44</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>388.07</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>428.44</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>386.18</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>428.44</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>428.44</v>
-      </c>
-      <c r="L20" s="1" t="n">
+      <c r="B21" s="1" t="n">
+        <v>3883.4</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>478.75</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>478.75</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>350.01</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>478.75</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>436.49</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>478.75</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>478.75</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>312.16</v>
       </c>
-      <c r="M20" s="1" t="n">
-        <v>340.68</v>
+      <c r="M21" s="1" t="n">
+        <v>390.99</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1307,44 +1307,87 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>203.6</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="D21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="G21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="L21" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="M21" t="n">
+        <v>22.62</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>3883.4</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>478.75</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>478.75</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>350.01</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>478.75</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>436.49</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>478.75</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>478.75</v>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>312.16</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>390.99</v>
+      <c r="B22" s="1" t="n">
+        <v>4087</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>372.63</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>459.11</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>501.37</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>334.78</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>413.61</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,44 +1350,87 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>246</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="D22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="H22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="I22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="L22" t="n">
+        <v>27.33</v>
+      </c>
+      <c r="M22" t="n">
+        <v>27.33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>4087</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>501.37</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>501.37</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>372.63</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>501.37</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>459.11</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>501.37</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>501.37</v>
-      </c>
-      <c r="L22" s="1" t="n">
-        <v>334.78</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>413.61</v>
+      <c r="B23" s="1" t="n">
+        <v>4333</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>528.71</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>528.71</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>399.96</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>528.71</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>486.44</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>528.71</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>528.71</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>362.11</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>440.94</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,44 +1393,87 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>153</v>
+      </c>
+      <c r="C23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="D23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="I23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19.12</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>19.12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>4333</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>528.71</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>528.71</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>399.96</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>528.71</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>486.44</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>528.71</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>528.71</v>
-      </c>
-      <c r="L23" s="1" t="n">
+      <c r="B24" s="1" t="n">
+        <v>4486</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>547.83</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>547.83</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>419.09</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>547.83</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>505.57</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>547.83</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>547.83</v>
+      </c>
+      <c r="L24" s="1" t="n">
         <v>362.11</v>
       </c>
-      <c r="M23" s="1" t="n">
-        <v>440.94</v>
+      <c r="M24" s="1" t="n">
+        <v>460.07</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,44 +1436,87 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>228.48</v>
+      </c>
+      <c r="C24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="D24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="G24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="H24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>28.56</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>28.56</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>4486</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>419.09</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>505.57</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>547.83</v>
-      </c>
-      <c r="L24" s="1" t="n">
+      <c r="B25" s="1" t="n">
+        <v>4714.48</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>576.39</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>576.39</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>447.65</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>576.39</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>534.13</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>576.39</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>576.39</v>
+      </c>
+      <c r="L25" s="1" t="n">
         <v>362.11</v>
       </c>
-      <c r="M24" s="1" t="n">
-        <v>460.07</v>
+      <c r="M25" s="1" t="n">
+        <v>488.63</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1479,44 +1479,87 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>172.56</v>
+      </c>
+      <c r="C25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="I25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="J25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="L25" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="M25" t="n">
+        <v>17.26</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>4714.48</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>576.39</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>576.39</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>447.65</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>576.39</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>534.13</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>576.39</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>576.39</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>362.11</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>488.63</v>
+      <c r="B26" s="1" t="n">
+        <v>4887.04</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>593.65</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>593.65</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>464.91</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>593.65</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <v>551.39</v>
+      </c>
+      <c r="I26" s="1" t="n">
+        <v>593.65</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>593.65</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>379.37</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>505.89</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,44 +1522,87 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>215.56</v>
+      </c>
+      <c r="C26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="D26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="G26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="I26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="J26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="K26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="L26" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="M26" t="n">
+        <v>21.56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>4887.04</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>593.65</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>593.65</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>464.91</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>593.65</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>551.39</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>593.65</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>17.26</v>
-      </c>
-      <c r="K26" s="1" t="n">
-        <v>593.65</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <v>379.37</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>505.89</v>
+      <c r="B27" s="1" t="n">
+        <v>5102.6</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>486.46</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>572.9400000000001</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>38.81</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>615.2</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>400.93</v>
+      </c>
+      <c r="M27" s="1" t="n">
+        <v>527.4400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1529,80 +1529,123 @@
         <v>215.56</v>
       </c>
       <c r="C26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="D26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="G26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="H26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="I26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="J26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="K26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
       <c r="L26" t="n">
-        <v>21.56</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>21.56</v>
+        <v>23.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>223.44</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="D27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="G27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="H27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="I27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="J27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="K27" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>24.83</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>5102.6</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>486.46</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="H27" s="1" t="n">
-        <v>572.9400000000001</v>
-      </c>
-      <c r="I27" s="1" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="J27" s="1" t="n">
-        <v>38.81</v>
-      </c>
-      <c r="K27" s="1" t="n">
-        <v>615.2</v>
-      </c>
-      <c r="L27" s="1" t="n">
-        <v>400.93</v>
-      </c>
-      <c r="M27" s="1" t="n">
-        <v>527.4400000000001</v>
+      <c r="B28" s="1" t="n">
+        <v>5326.04</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>642.4299999999999</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>642.4299999999999</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>513.6799999999999</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>642.4299999999999</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>600.16</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>642.4299999999999</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>66.03</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>642.4299999999999</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>379.37</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>554.66</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,44 +1608,87 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>141.76</v>
+      </c>
+      <c r="C28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="D28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="H28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="I28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="J28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="K28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="L28" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="M28" t="n">
+        <v>14.18</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>5326.04</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>642.4299999999999</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>642.4299999999999</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>513.6799999999999</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>642.4299999999999</v>
-      </c>
-      <c r="H28" s="1" t="n">
-        <v>600.16</v>
-      </c>
-      <c r="I28" s="1" t="n">
-        <v>642.4299999999999</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>66.03</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>642.4299999999999</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>379.37</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>554.66</v>
+      <c r="B29" s="1" t="n">
+        <v>5467.8</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>527.86</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <v>614.34</v>
+      </c>
+      <c r="I29" s="1" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>80.20999999999999</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>656.6</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>393.55</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>568.84</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1357,37 +1357,37 @@
         <v>246</v>
       </c>
       <c r="C22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="D22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="G22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="H22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="I22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
       <c r="L22" t="n">
-        <v>27.33</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>27.33</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="23">
@@ -1615,80 +1615,123 @@
         <v>141.76</v>
       </c>
       <c r="C28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="D28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="G28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="H28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="I28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="J28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="K28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
       <c r="L28" t="n">
-        <v>14.18</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>14.18</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>200.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="H29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="L29" t="n">
+        <v>20.02</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20.02</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>5467.8</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>656.6</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>656.6</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>527.86</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>656.6</v>
-      </c>
-      <c r="H29" s="1" t="n">
-        <v>614.34</v>
-      </c>
-      <c r="I29" s="1" t="n">
-        <v>656.6</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>80.20999999999999</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>656.6</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>393.55</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>568.84</v>
+      <c r="B30" s="1" t="n">
+        <v>5668</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>552.87</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <v>639.35</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>681.61</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>593.85</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,44 +1694,87 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>251.12</v>
+      </c>
+      <c r="C30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="H30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="I30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="J30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="K30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="L30" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>25.11</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>5668</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>681.61</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>681.61</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>552.87</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>681.61</v>
-      </c>
-      <c r="H30" s="1" t="n">
-        <v>639.35</v>
-      </c>
-      <c r="I30" s="1" t="n">
-        <v>681.61</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>681.61</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>372.06</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>593.85</v>
+      <c r="B31" s="1" t="n">
+        <v>5919.12</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>706.72</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>706.72</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>577.98</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>706.72</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>664.46</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>706.72</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>126.92</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>706.72</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>397.17</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>618.96</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1737,44 +1737,87 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>189.52</v>
+      </c>
+      <c r="C31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="D31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="G31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="H31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="I31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="J31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="K31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="L31" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="M31" t="n">
+        <v>18.95</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>5919.12</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>706.72</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>706.72</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>577.98</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>706.72</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>664.46</v>
-      </c>
-      <c r="I31" s="1" t="n">
-        <v>706.72</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>126.92</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>706.72</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>397.17</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>618.96</v>
+      <c r="B32" s="1" t="n">
+        <v>6108.64</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>725.6799999999999</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>725.6799999999999</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>596.9299999999999</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>725.6799999999999</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <v>683.41</v>
+      </c>
+      <c r="I32" s="1" t="n">
+        <v>725.6799999999999</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>145.87</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>725.6799999999999</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>416.12</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>637.92</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,44 +533,87 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>236.48</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="H3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="M3" t="n">
+        <v>23.65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>493.72</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="B4" s="1" t="n">
+        <v>730.2</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>49.37</v>
+      <c r="F4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>73.02</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>73.02</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,44 +576,87 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>487.36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="D4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="I4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="J4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="K4" t="n">
+        <v>54.15</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>54.15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>730.2</v>
-      </c>
-      <c r="C4" s="1" t="n">
+      <c r="B5" s="1" t="n">
+        <v>1217.56</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>127.17</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>73.02</v>
+      <c r="M5" s="1" t="n">
+        <v>127.17</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,44 +619,87 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>192.56</v>
+      </c>
+      <c r="C5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>1217.56</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="E5" s="1" t="n">
+      <c r="B6" s="1" t="n">
+        <v>1410.12</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="E6" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>127.17</v>
-      </c>
-      <c r="L5" s="1" t="n">
+      <c r="F6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M5" s="1" t="n">
-        <v>127.17</v>
+      <c r="M6" s="1" t="n">
+        <v>148.57</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,44 +662,87 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="C6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>1410.12</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>148.57</v>
-      </c>
-      <c r="L6" s="1" t="n">
+      <c r="B7" s="1" t="n">
+        <v>1547.8</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="L7" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M6" s="1" t="n">
-        <v>148.57</v>
+      <c r="M7" s="1" t="n">
+        <v>163.86</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,44 +705,87 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>260.4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="D7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="G7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="J7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>32.55</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>1547.8</v>
-      </c>
-      <c r="C7" s="1" t="n">
+      <c r="B8" s="1" t="n">
+        <v>1808.2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="H8" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="L7" s="1" t="n">
+      <c r="I8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="L8" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M7" s="1" t="n">
-        <v>163.86</v>
+      <c r="M8" s="1" t="n">
+        <v>196.41</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,44 +748,87 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>223.04</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>27.88</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>1808.2</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="G8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="H8" s="1" t="n">
+      <c r="B9" s="1" t="n">
+        <v>2031.24</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <v>196.41</v>
-      </c>
-      <c r="L8" s="1" t="n">
+      <c r="I9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>224.29</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M8" s="1" t="n">
-        <v>196.41</v>
+      <c r="M9" s="1" t="n">
+        <v>224.29</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,44 +791,87 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>156.16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="K9" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19.52</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>2031.24</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="H9" s="1" t="n">
+      <c r="B10" s="1" t="n">
+        <v>2187.4</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="H10" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>224.29</v>
-      </c>
-      <c r="L9" s="1" t="n">
+      <c r="I10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>243.81</v>
+      </c>
+      <c r="L10" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M9" s="1" t="n">
-        <v>224.29</v>
+      <c r="M10" s="1" t="n">
+        <v>243.81</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -877,44 +877,87 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>285.08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="D11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="G11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="J11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>35.63</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>35.63</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>2649.84</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="H11" s="1" t="n">
+      <c r="B12" s="1" t="n">
+        <v>2934.92</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="H12" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>301.62</v>
-      </c>
-      <c r="L11" s="1" t="n">
+      <c r="I12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>337.25</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M11" s="1" t="n">
-        <v>301.62</v>
+      <c r="M12" s="1" t="n">
+        <v>337.25</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,44 +920,87 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>125.24</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>15.65</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>2934.92</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="H12" s="1" t="n">
+      <c r="B13" s="1" t="n">
+        <v>3060.16</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="H13" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>337.25</v>
-      </c>
-      <c r="L12" s="1" t="n">
+      <c r="I13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="L13" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M12" s="1" t="n">
-        <v>337.25</v>
+      <c r="M13" s="1" t="n">
+        <v>352.91</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -963,44 +963,87 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="C13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>3060.16</v>
-      </c>
-      <c r="C13" s="1" t="n">
+      <c r="B14" s="1" t="n">
+        <v>3212.04</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <v>163.86</v>
+      </c>
+      <c r="I14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="J14" s="1" t="n">
         <v>352.91</v>
       </c>
-      <c r="D13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="L13" s="1" t="n">
+      <c r="K14" s="1" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="L14" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M13" s="1" t="n">
-        <v>352.91</v>
+      <c r="M14" s="1" t="n">
+        <v>374.61</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1006,44 +1006,87 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>275.52</v>
+      </c>
+      <c r="C14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="D14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="G14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>39.36</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>39.36</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>3212.04</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="H14" s="1" t="n">
+      <c r="B15" s="1" t="n">
+        <v>3487.56</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="H15" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="J14" s="1" t="n">
+      <c r="I15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="J15" s="1" t="n">
         <v>352.91</v>
       </c>
-      <c r="K14" s="1" t="n">
-        <v>374.61</v>
-      </c>
-      <c r="L14" s="1" t="n">
+      <c r="K15" s="1" t="n">
+        <v>413.97</v>
+      </c>
+      <c r="L15" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M14" s="1" t="n">
-        <v>374.61</v>
+      <c r="M15" s="1" t="n">
+        <v>413.97</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,44 +1049,87 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>146.96</v>
+      </c>
+      <c r="C15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="G15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>3487.56</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="G15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="H15" s="1" t="n">
+      <c r="B16" s="1" t="n">
+        <v>3634.52</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="H16" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="J15" s="1" t="n">
+      <c r="I16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="J16" s="1" t="n">
         <v>352.91</v>
       </c>
-      <c r="K15" s="1" t="n">
-        <v>413.97</v>
-      </c>
-      <c r="L15" s="1" t="n">
+      <c r="K16" s="1" t="n">
+        <v>434.96</v>
+      </c>
+      <c r="L16" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M15" s="1" t="n">
-        <v>413.97</v>
+      <c r="M16" s="1" t="n">
+        <v>434.96</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,44 +1092,87 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>144.28</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="D16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="G16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20.61</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>20.61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>3634.52</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="G16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="H16" s="1" t="n">
+      <c r="B17" s="1" t="n">
+        <v>3778.8</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="H17" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="J16" s="1" t="n">
+      <c r="I17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="J17" s="1" t="n">
         <v>352.91</v>
       </c>
-      <c r="K16" s="1" t="n">
-        <v>434.96</v>
-      </c>
-      <c r="L16" s="1" t="n">
+      <c r="K17" s="1" t="n">
+        <v>455.57</v>
+      </c>
+      <c r="L17" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M16" s="1" t="n">
-        <v>434.96</v>
+      <c r="M17" s="1" t="n">
+        <v>455.57</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,44 +1135,87 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>471.12</v>
+      </c>
+      <c r="C17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="D17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="G17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="J17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="K17" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>58.89</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>3778.8</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="H17" s="1" t="n">
+      <c r="B18" s="1" t="n">
+        <v>4249.92</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="H18" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>352.91</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>455.57</v>
-      </c>
-      <c r="L17" s="1" t="n">
+      <c r="I18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>411.8</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>514.46</v>
+      </c>
+      <c r="L18" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M17" s="1" t="n">
-        <v>455.57</v>
+      <c r="M18" s="1" t="n">
+        <v>514.46</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,44 +1178,87 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>337.6</v>
+      </c>
+      <c r="C18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>4249.92</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="G18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="H18" s="1" t="n">
+      <c r="B19" s="1" t="n">
+        <v>4587.52</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="H19" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>411.8</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>514.46</v>
-      </c>
-      <c r="L18" s="1" t="n">
+      <c r="I19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>454</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>556.66</v>
+      </c>
+      <c r="L19" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M18" s="1" t="n">
-        <v>514.46</v>
+      <c r="M19" s="1" t="n">
+        <v>556.66</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1221,44 +1221,87 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="C19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="G19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="J19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>12.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>4587.52</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="H19" s="1" t="n">
+      <c r="B20" s="1" t="n">
+        <v>4684.44</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="H20" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>454</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>556.66</v>
-      </c>
-      <c r="L19" s="1" t="n">
+      <c r="I20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>466.11</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>568.78</v>
+      </c>
+      <c r="L20" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>556.66</v>
+      <c r="M20" s="1" t="n">
+        <v>568.78</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1264,44 +1264,87 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>129.44</v>
+      </c>
+      <c r="C20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="J20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="K20" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>16.18</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>4684.44</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="H20" s="1" t="n">
+      <c r="B21" s="1" t="n">
+        <v>4813.88</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="H21" s="1" t="n">
         <v>163.86</v>
       </c>
-      <c r="I20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>466.11</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>568.78</v>
-      </c>
-      <c r="L20" s="1" t="n">
+      <c r="I21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>482.29</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>584.96</v>
+      </c>
+      <c r="L21" s="1" t="n">
         <v>73.02</v>
       </c>
-      <c r="M20" s="1" t="n">
-        <v>568.78</v>
+      <c r="M21" s="1" t="n">
+        <v>584.96</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,37 +497,37 @@
         <v>493.72</v>
       </c>
       <c r="C2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="D2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="G2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="H2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="I2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="J2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="K2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
       <c r="L2" t="n">
-        <v>49.37</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>49.37</v>
+        <v>54.86</v>
       </c>
     </row>
     <row r="3">
@@ -540,37 +540,37 @@
         <v>236.48</v>
       </c>
       <c r="C3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="D3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="G3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="H3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="I3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="J3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="K3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
       <c r="L3" t="n">
-        <v>23.65</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>23.65</v>
+        <v>26.28</v>
       </c>
     </row>
     <row r="4">
@@ -1307,44 +1307,87 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>114.36</v>
+      </c>
+      <c r="C21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="D21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="J21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>14.29</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>4813.88</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>163.86</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>482.29</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>584.96</v>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>73.02</v>
-      </c>
-      <c r="M21" s="1" t="n">
-        <v>584.96</v>
+      <c r="B22" s="1" t="n">
+        <v>4928.24</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>171.98</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>504.7</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>607.37</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="1" t="n">
+        <v>607.37</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1350,44 +1350,87 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="C22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="K22" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>4928.24</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="H22" s="1" t="n">
+      <c r="B23" s="1" t="n">
+        <v>5078.64</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="H23" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>504.7</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>607.37</v>
-      </c>
-      <c r="L22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="1" t="n">
-        <v>607.37</v>
+      <c r="I23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>523.5</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>626.17</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>626.17</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,44 +1393,87 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>235</v>
+      </c>
+      <c r="C23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="D23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="G23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="J23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="K23" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>29.38</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>5078.64</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="H23" s="1" t="n">
+      <c r="B24" s="1" t="n">
+        <v>5313.64</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="H24" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>523.5</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>626.17</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1" t="n">
-        <v>626.17</v>
+      <c r="I24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>552.88</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>655.54</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1" t="n">
+        <v>655.54</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,44 +1436,130 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>295.72</v>
+      </c>
+      <c r="C24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="D24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="G24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="J24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="K24" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>36.97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>300.92</v>
+      </c>
+      <c r="C25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="D25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="G25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="J25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="K25" t="n">
+        <v>37.62</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>37.62</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>5313.64</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="H24" s="1" t="n">
+      <c r="B26" s="1" t="n">
+        <v>5910.28</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="G26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="H26" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>552.88</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>655.54</v>
-      </c>
-      <c r="L24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="1" t="n">
-        <v>655.54</v>
+      <c r="I26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="J26" s="1" t="n">
+        <v>627.46</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>730.12</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>730.12</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,44 +1522,130 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>225</v>
+      </c>
+      <c r="C26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="D26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="K26" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>28.12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>110.24</v>
+      </c>
+      <c r="C27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="D27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="J27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="K27" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>13.78</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>5910.28</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="H26" s="1" t="n">
+      <c r="B28" s="1" t="n">
+        <v>6245.52</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="G28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="H28" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>627.46</v>
-      </c>
-      <c r="K26" s="1" t="n">
-        <v>730.12</v>
-      </c>
-      <c r="L26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1" t="n">
-        <v>730.12</v>
+      <c r="I28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>669.36</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <v>772.03</v>
+      </c>
+      <c r="L28" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1" t="n">
+        <v>772.03</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,44 +1608,87 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="G28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>6245.52</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="H28" s="1" t="n">
+      <c r="B29" s="1" t="n">
+        <v>6472.72</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="G29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="H29" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="J28" s="1" t="n">
-        <v>669.36</v>
-      </c>
-      <c r="K28" s="1" t="n">
-        <v>772.03</v>
-      </c>
-      <c r="L28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>772.03</v>
+      <c r="I29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="J29" s="1" t="n">
+        <v>697.76</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <v>800.4299999999999</v>
+      </c>
+      <c r="L29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1" t="n">
+        <v>800.4299999999999</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,44 +1651,87 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>164.2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="D29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="K29" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>6472.72</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="H29" s="1" t="n">
+      <c r="B30" s="1" t="n">
+        <v>6636.92</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="H30" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="J29" s="1" t="n">
-        <v>697.76</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>800.4299999999999</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1" t="n">
-        <v>800.4299999999999</v>
+      <c r="I30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>718.29</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <v>820.95</v>
+      </c>
+      <c r="L30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1" t="n">
+        <v>820.95</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1694,44 +1694,87 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>225.64</v>
+      </c>
+      <c r="C30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="G30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>6636.92</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="H30" s="1" t="n">
+      <c r="B31" s="1" t="n">
+        <v>6862.56</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="H31" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>718.29</v>
-      </c>
-      <c r="K30" s="1" t="n">
-        <v>820.95</v>
-      </c>
-      <c r="L30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1" t="n">
-        <v>820.95</v>
+      <c r="I31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>746.49</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>849.16</v>
+      </c>
+      <c r="L31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1" t="n">
+        <v>849.16</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1737,44 +1737,87 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>350.64</v>
+      </c>
+      <c r="C31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="D31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="G31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="J31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="K31" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>43.83</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>6862.56</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="H31" s="1" t="n">
+      <c r="B32" s="1" t="n">
+        <v>7213.2</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="G32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="H32" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="J31" s="1" t="n">
-        <v>746.49</v>
-      </c>
-      <c r="K31" s="1" t="n">
-        <v>849.16</v>
-      </c>
-      <c r="L31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1" t="n">
-        <v>849.16</v>
+      <c r="I32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="J32" s="1" t="n">
+        <v>790.3200000000001</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <v>892.99</v>
+      </c>
+      <c r="L32" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="1" t="n">
+        <v>892.99</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,44 +1780,87 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>270.28</v>
+      </c>
+      <c r="C32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="D32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="G32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="J32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="K32" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>33.78</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>7213.2</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="H32" s="1" t="n">
+      <c r="B33" s="1" t="n">
+        <v>7483.48</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="G33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="H33" s="1" t="n">
         <v>171.98</v>
       </c>
-      <c r="I32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="J32" s="1" t="n">
-        <v>790.3200000000001</v>
-      </c>
-      <c r="K32" s="1" t="n">
-        <v>892.99</v>
-      </c>
-      <c r="L32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>892.99</v>
+      <c r="I33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="J33" s="1" t="n">
+        <v>824.11</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>926.77</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>926.77</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -525,41 +525,81 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>161.04</v>
+      </c>
+      <c r="C3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="D3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="K3" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="L3" t="n">
+        <v>23.01</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>196.76</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="G3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="H3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="K3" s="1" t="n">
-        <v>28.11</v>
-      </c>
-      <c r="L3" s="1" t="n">
-        <v>28.11</v>
+      <c r="B4" s="1" t="n">
+        <v>357.8</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>51.11</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>51.11</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,41 +565,81 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>272.4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="D4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="G4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>38.91</v>
+      </c>
+      <c r="L4" t="n">
+        <v>38.91</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>357.8</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="G4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="K4" s="1" t="n">
-        <v>51.11</v>
-      </c>
-      <c r="L4" s="1" t="n">
-        <v>51.11</v>
+      <c r="B5" s="1" t="n">
+        <v>630.2</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>90.03</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>90.03</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,41 +605,81 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>375.8</v>
+      </c>
+      <c r="C5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="D5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="G5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="K5" t="n">
+        <v>53.69</v>
+      </c>
+      <c r="L5" t="n">
+        <v>53.69</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>630.2</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="G5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="H5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>90.03</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>90.03</v>
+      <c r="B6" s="1" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>143.71</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>143.71</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,41 +645,81 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>331.72</v>
+      </c>
+      <c r="C6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="D6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="G6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="H6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="K6" t="n">
+        <v>41.47</v>
+      </c>
+      <c r="L6" t="n">
+        <v>41.47</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>1006</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="G6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="H6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <v>143.71</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <v>143.71</v>
+      <c r="B7" s="1" t="n">
+        <v>1337.72</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>41.46</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>185.18</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>185.18</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -685,41 +685,121 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>348.16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="D7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="G7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="H7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="K7" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="L7" t="n">
+        <v>43.52</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>220.76</v>
+      </c>
+      <c r="C8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="D8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="H8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="K8" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>27.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>1337.72</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="G7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <v>185.18</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <v>185.18</v>
+      <c r="B9" s="1" t="n">
+        <v>1906.64</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>112.58</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>256.29</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>256.29</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,41 +765,81 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>131.36</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16.42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16.42</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>1906.64</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="G9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>112.58</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>256.29</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>256.29</v>
+      <c r="B10" s="1" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>272.71</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>272.71</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,41 +805,81 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>151.88</v>
+      </c>
+      <c r="C10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="H10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>18.98</v>
+      </c>
+      <c r="L10" t="n">
+        <v>18.98</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>2038</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="G10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>129</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <v>272.71</v>
-      </c>
-      <c r="L10" s="1" t="n">
-        <v>272.71</v>
+      <c r="B11" s="1" t="n">
+        <v>2189.88</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>147.99</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>291.7</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>291.7</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -845,41 +845,81 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>228.6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="D11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="H11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="K11" t="n">
+        <v>28.57</v>
+      </c>
+      <c r="L11" t="n">
+        <v>28.57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>2189.88</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>147.99</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="K11" s="1" t="n">
-        <v>291.7</v>
-      </c>
-      <c r="L11" s="1" t="n">
-        <v>291.7</v>
+      <c r="B12" s="1" t="n">
+        <v>2418.48</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>176.56</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="L12" s="1" t="n">
+        <v>320.27</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,41 +885,81 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>127.28</v>
+      </c>
+      <c r="C12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="D12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="H12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="L12" t="n">
+        <v>15.91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>2418.48</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="H12" s="1" t="n">
-        <v>176.56</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="K12" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="L12" s="1" t="n">
-        <v>320.27</v>
+      <c r="B13" s="1" t="n">
+        <v>2545.76</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>192.47</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>336.18</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>336.18</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,74 +892,194 @@
         <v>127.28</v>
       </c>
       <c r="C12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="D12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>15.91</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="H12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="K12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
       <c r="L12" t="n">
-        <v>15.91</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>311.04</v>
+      </c>
+      <c r="C13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="D13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="H13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="K13" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="L13" t="n">
+        <v>44.43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>78.44</v>
+      </c>
+      <c r="C14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="H14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="K14" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="L14" t="n">
+        <v>11.21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>313</v>
+      </c>
+      <c r="C15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="D15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="H15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="K15" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="L15" t="n">
+        <v>44.71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>2545.76</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>192.47</v>
-      </c>
-      <c r="I13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="K13" s="1" t="n">
-        <v>336.18</v>
-      </c>
-      <c r="L13" s="1" t="n">
-        <v>336.18</v>
+      <c r="B16" s="1" t="n">
+        <v>3248.24</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>438.81</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>438.81</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>320.27</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>438.81</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>295.1</v>
+      </c>
+      <c r="I16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="1" t="n">
+        <v>438.81</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <v>438.81</v>
+      </c>
+      <c r="L16" s="1" t="n">
+        <v>438.81</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,41 +1045,81 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>204.12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="D16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="H16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="K16" t="n">
+        <v>29.16</v>
+      </c>
+      <c r="L16" t="n">
+        <v>29.16</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>3248.24</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>438.81</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>438.81</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="n">
+      <c r="B17" s="1" t="n">
+        <v>3452.36</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>467.97</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>467.97</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="n">
         <v>320.27</v>
       </c>
-      <c r="G16" s="1" t="n">
-        <v>438.81</v>
-      </c>
-      <c r="H16" s="1" t="n">
-        <v>295.1</v>
-      </c>
-      <c r="I16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1" t="n">
-        <v>438.81</v>
-      </c>
-      <c r="K16" s="1" t="n">
-        <v>438.81</v>
-      </c>
-      <c r="L16" s="1" t="n">
-        <v>438.81</v>
+      <c r="G17" s="1" t="n">
+        <v>467.97</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>324.26</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>467.97</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>467.97</v>
+      </c>
+      <c r="L17" s="1" t="n">
+        <v>467.97</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1085,41 +1085,81 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>119.48</v>
+      </c>
+      <c r="C17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="D17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="H17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="K17" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17.07</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>3452.36</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>467.97</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>467.97</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="n">
+      <c r="B18" s="1" t="n">
+        <v>3571.84</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
         <v>320.27</v>
       </c>
-      <c r="G17" s="1" t="n">
-        <v>467.97</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>324.26</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>467.97</v>
-      </c>
-      <c r="K17" s="1" t="n">
-        <v>467.97</v>
-      </c>
-      <c r="L17" s="1" t="n">
-        <v>467.97</v>
+      <c r="G18" s="1" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>341.33</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>485.04</v>
+      </c>
+      <c r="L18" s="1" t="n">
+        <v>485.04</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1125,41 +1125,81 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>150.48</v>
+      </c>
+      <c r="C18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>3571.84</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>485.04</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>485.04</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="1" t="n">
+      <c r="B19" s="1" t="n">
+        <v>3722.32</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>506.54</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>506.54</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="1" t="n">
         <v>320.27</v>
       </c>
-      <c r="G18" s="1" t="n">
-        <v>485.04</v>
-      </c>
-      <c r="H18" s="1" t="n">
-        <v>341.33</v>
-      </c>
-      <c r="I18" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="1" t="n">
-        <v>485.04</v>
-      </c>
-      <c r="K18" s="1" t="n">
-        <v>485.04</v>
-      </c>
-      <c r="L18" s="1" t="n">
-        <v>485.04</v>
+      <c r="G19" s="1" t="n">
+        <v>506.54</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>506.54</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>506.54</v>
+      </c>
+      <c r="L19" s="1" t="n">
+        <v>506.54</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,41 +1165,81 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>164</v>
+      </c>
+      <c r="C19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>3722.32</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>506.54</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>506.54</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>320.27</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>506.54</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>362.82</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>506.54</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>506.54</v>
-      </c>
-      <c r="L19" s="1" t="n">
-        <v>506.54</v>
+      <c r="B20" s="1" t="n">
+        <v>3886.32</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>527.04</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>527.04</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>340.77</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>527.04</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>383.32</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>527.04</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>527.04</v>
+      </c>
+      <c r="L20" s="1" t="n">
+        <v>527.04</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,41 +1205,81 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>110.28</v>
+      </c>
+      <c r="C20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="K20" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13.79</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>3886.32</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>527.04</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>527.04</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>340.77</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>527.04</v>
-      </c>
-      <c r="H20" s="1" t="n">
-        <v>383.32</v>
-      </c>
-      <c r="I20" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1" t="n">
-        <v>527.04</v>
-      </c>
-      <c r="K20" s="1" t="n">
-        <v>527.04</v>
-      </c>
-      <c r="L20" s="1" t="n">
-        <v>527.04</v>
+      <c r="B21" s="1" t="n">
+        <v>3996.6</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>354.56</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>397.11</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="L21" s="1" t="n">
+        <v>540.8200000000001</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1245,41 +1245,81 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>284.32</v>
+      </c>
+      <c r="C21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="D21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="H21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="K21" t="n">
+        <v>35.54</v>
+      </c>
+      <c r="L21" t="n">
+        <v>35.54</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>3996.6</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>354.56</v>
-      </c>
-      <c r="G21" s="1" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="H21" s="1" t="n">
-        <v>397.11</v>
-      </c>
-      <c r="I21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="K21" s="1" t="n">
-        <v>540.8200000000001</v>
-      </c>
-      <c r="L21" s="1" t="n">
-        <v>540.8200000000001</v>
+      <c r="B22" s="1" t="n">
+        <v>4280.92</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>576.36</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>576.36</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>390.1</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>576.36</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <v>432.65</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="1" t="n">
+        <v>576.36</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <v>576.36</v>
+      </c>
+      <c r="L22" s="1" t="n">
+        <v>576.36</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1285,41 +1285,81 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>407.16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>4280.92</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>576.36</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>576.36</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>390.1</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>576.36</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>432.65</v>
-      </c>
-      <c r="I22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1" t="n">
-        <v>576.36</v>
-      </c>
-      <c r="K22" s="1" t="n">
-        <v>576.36</v>
-      </c>
-      <c r="L22" s="1" t="n">
-        <v>576.36</v>
+      <c r="B23" s="1" t="n">
+        <v>4688.08</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>627.26</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>627.26</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="1" t="n">
+        <v>440.99</v>
+      </c>
+      <c r="G23" s="1" t="n">
+        <v>627.26</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>483.54</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1" t="n">
+        <v>627.26</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <v>627.26</v>
+      </c>
+      <c r="L23" s="1" t="n">
+        <v>627.26</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1325,41 +1325,81 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>76.16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="D23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="H23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="K23" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="L23" t="n">
+        <v>9.52</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>4688.08</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>627.26</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>627.26</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>440.99</v>
-      </c>
-      <c r="G23" s="1" t="n">
-        <v>627.26</v>
-      </c>
-      <c r="H23" s="1" t="n">
-        <v>483.54</v>
-      </c>
-      <c r="I23" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1" t="n">
-        <v>627.26</v>
-      </c>
-      <c r="K23" s="1" t="n">
-        <v>627.26</v>
-      </c>
-      <c r="L23" s="1" t="n">
-        <v>627.26</v>
+      <c r="B24" s="1" t="n">
+        <v>4764.24</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>636.78</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>636.78</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="1" t="n">
+        <v>450.51</v>
+      </c>
+      <c r="G24" s="1" t="n">
+        <v>636.78</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <v>493.06</v>
+      </c>
+      <c r="I24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1" t="n">
+        <v>636.78</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <v>636.78</v>
+      </c>
+      <c r="L24" s="1" t="n">
+        <v>636.78</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,41 +1365,81 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="C24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="D24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="K24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="L24" t="n">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>4764.24</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>636.78</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>636.78</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>450.51</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>636.78</v>
-      </c>
-      <c r="H24" s="1" t="n">
-        <v>493.06</v>
-      </c>
-      <c r="I24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1" t="n">
-        <v>636.78</v>
-      </c>
-      <c r="K24" s="1" t="n">
-        <v>636.78</v>
-      </c>
-      <c r="L24" s="1" t="n">
-        <v>636.78</v>
+      <c r="B25" s="1" t="n">
+        <v>4852.32</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>647.79</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>647.79</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="1" t="n">
+        <v>461.52</v>
+      </c>
+      <c r="G25" s="1" t="n">
+        <v>647.79</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <v>504.07</v>
+      </c>
+      <c r="I25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="n">
+        <v>647.79</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>647.79</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>647.79</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_comissao.xlsx
+++ b/relatorio_comissao.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,81 +1365,161 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88.08</v>
+        <v>148.24</v>
       </c>
       <c r="C24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="D24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="G24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="H24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="K24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
       <c r="L24" t="n">
-        <v>11.01</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>88.08</v>
+      </c>
+      <c r="C25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="D25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="K25" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="L25" t="n">
+        <v>11.01</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>189.08</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="D26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="H26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="K26" t="n">
+        <v>23.64</v>
+      </c>
+      <c r="L26" t="n">
+        <v>23.64</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>4852.32</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>647.79</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>647.79</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>461.52</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>647.79</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>504.07</v>
-      </c>
-      <c r="I25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>647.79</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>647.79</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>647.79</v>
+      <c r="B27" s="1" t="n">
+        <v>5189.64</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>689.95</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>689.95</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1" t="n">
+        <v>503.69</v>
+      </c>
+      <c r="G27" s="1" t="n">
+        <v>689.95</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <v>546.24</v>
+      </c>
+      <c r="I27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1" t="n">
+        <v>689.95</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <v>689.95</v>
+      </c>
+      <c r="L27" s="1" t="n">
+        <v>689.95</v>
       </c>
     </row>
   </sheetData>
